--- a/tiflow-chargeitem/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERPCHRG-PR-ChargeItem.xlsx
+++ b/tiflow-chargeitem/develop/2.0.0-ballot.2/StructureDefinition-GEM-ERPCHRG-PR-ChargeItem.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4023" uniqueCount="584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4042" uniqueCount="599">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2028-04-01</t>
+    <t>2026-06-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -439,6 +439,9 @@
 </t>
   </si>
   <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
     <t>closed</t>
   </si>
   <si>
@@ -465,56 +468,59 @@
     <t>Optional Extension for ChargeItem-Ressources in eRx workflow</t>
   </si>
   <si>
+    <t>ChargeItem.modifierExtension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t>Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
+  </si>
+  <si>
+    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
+  </si>
+  <si>
+    <t>open</t>
+  </si>
+  <si>
+    <t>DomainResource.modifierExtension</t>
+  </si>
+  <si>
+    <t>ChargeItem.identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
+</t>
+  </si>
+  <si>
+    <t>Business Identifier for item</t>
+  </si>
+  <si>
+    <t>Identifiers assigned to this event performer or other systems.</t>
+  </si>
+  <si>
+    <t>Allows identification of the charge Item as it is known by various participating systems and in a way that remains consistent across servers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:system}
+</t>
+  </si>
+  <si>
+    <t>The task ressource contains three identifier. The first one is the identifier for the ask representing one e-prescription. The other identifier are representing the patient as owner of the prescription. One is the "Krankenversichertennummer" which identify each patient by his health insurance company and the other is "Institutionskennzeichen".</t>
+  </si>
+  <si>
     <t xml:space="preserve">ele-1
 </t>
   </si>
   <si>
-    <t>ChargeItem.modifierExtension</t>
-  </si>
-  <si>
-    <t>extensions
-user content</t>
-  </si>
-  <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
-Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
-  </si>
-  <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4/extensibility.html#modifierExtension).</t>
-  </si>
-  <si>
-    <t>DomainResource.modifierExtension</t>
-  </si>
-  <si>
-    <t>ChargeItem.identifier</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Identifier
-</t>
-  </si>
-  <si>
-    <t>Business Identifier for item</t>
-  </si>
-  <si>
-    <t>Identifiers assigned to this event performer or other systems.</t>
-  </si>
-  <si>
-    <t>Allows identification of the charge Item as it is known by various participating systems and in a way that remains consistent across servers.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:system}
-</t>
-  </si>
-  <si>
-    <t>The task ressource contains three identifier. The first one is the identifier for the ask representing one e-prescription. The other identifier are representing the patient as owner of the prescription. One is the "Krankenversichertennummer" which identify each patient by his health insurance company and the other is "Institutionskennzeichen".</t>
-  </si>
-  <si>
     <t>Event.identifier</t>
   </si>
   <si>
@@ -573,12 +579,6 @@
     <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>open</t>
-  </si>
-  <si>
     <t>Element.extension</t>
   </si>
   <si>
@@ -728,7 +728,15 @@
     <t>Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
+    <t>A Period specifies a range of time; the context of use will specify whether the entire range applies (e.g. "the patient was an inpatient of the hospital for this time range") or one value from the range applies (e.g. "give to the patient between these two times").
+Period is not used for a duration (a measure of elapsed time). See [Duration](http://hl7.org/fhir/R4/datatypes.html#Duration).</t>
+  </si>
+  <si>
     <t>Identifier.period</t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+per-1:If present, start SHALL have a lower value than end {start.hasValue().not() or end.hasValue().not() or (start &lt;= end)}</t>
   </si>
   <si>
     <t>CX.7 + CX.8</t>
@@ -759,6 +767,10 @@
     <t>Identifier.assigner</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
+  </si>
+  <si>
     <t>CX.4 / (CX.4,CX.9,CX.10)</t>
   </si>
   <si>
@@ -811,6 +823,9 @@
   </si>
   <si>
     <t>References the (external) source of pricing information, rules of application for the code this ChargeItem uses.</t>
+  </si>
+  <si>
+    <t>see http://en.wikipedia.org/wiki/Uniform_resource_identifier</t>
   </si>
   <si>
     <t>Event.instantiates</t>
@@ -835,6 +850,9 @@
     <t>References the source of pricing information, rules of application for the code this ChargeItem uses.</t>
   </si>
   <si>
+    <t>see [Canonical References](http://hl7.org/fhir/R4/references.html#canonical)</t>
+  </si>
+  <si>
     <t>ChargeItem.status</t>
   </si>
   <si>
@@ -883,6 +901,9 @@
     <t>ChargeItems can be grouped to larger ChargeItems covering the whole set.</t>
   </si>
   <si>
+    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
+  </si>
+  <si>
     <t>E.g. Drug administration as part of a procedure, procedure as part of observation, etc.</t>
   </si>
   <si>
@@ -905,6 +926,9 @@
     <t>A code that identifies the charge, like a billing code.</t>
   </si>
   <si>
+    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+  </si>
+  <si>
     <t>example</t>
   </si>
   <si>
@@ -1045,6 +1069,9 @@
   </si>
   <si>
     <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
+  </si>
+  <si>
+    <t>Note that FHIR strings SHALL NOT exceed 1MB in size</t>
   </si>
   <si>
     <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
@@ -1212,6 +1239,9 @@
     <t>Reference.identifier</t>
   </si>
   <si>
+    <t>CX / EI (occasionally, more often EI maps to a resource id or a URL)</t>
+  </si>
+  <si>
     <t>ChargeItem.subject.display</t>
   </si>
   <si>
@@ -1418,6 +1448,9 @@
     <t>FT1.13</t>
   </si>
   <si>
+    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
+  </si>
+  <si>
     <t>ChargeItem.quantity</t>
   </si>
   <si>
@@ -1434,9 +1467,16 @@
     <t>In many cases this may just be a value, if the underlying units are implicit in the definition of the charge item code.</t>
   </si>
   <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}</t>
+  </si>
+  <si>
     <t>FT1.10</t>
   </si>
   <si>
+    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
+  </si>
+  <si>
     <t>ChargeItem.bodysite</t>
   </si>
   <si>
@@ -1453,6 +1493,9 @@
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
+  </si>
+  <si>
+    <t>CE/CNE/CWE</t>
   </si>
   <si>
     <t>.targetBodySiteCode</t>
@@ -1496,6 +1539,9 @@
     <t>FT1.22</t>
   </si>
   <si>
+    <t>MO</t>
+  </si>
+  <si>
     <t>ChargeItem.overrideReason</t>
   </si>
   <si>
@@ -1660,6 +1706,9 @@
   </si>
   <si>
     <t>Comments made about the event by the performer, subject or other participants.</t>
+  </si>
+  <si>
+    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
   </si>
   <si>
     <t>Event.note</t>
@@ -2184,7 +2233,7 @@
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="39.109375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="53.91015625" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="87.9765625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
@@ -3180,15 +3229,17 @@
       <c r="AB9" t="s" s="2">
         <v>135</v>
       </c>
-      <c r="AC9" s="2"/>
+      <c r="AC9" t="s" s="2">
+        <v>136</v>
+      </c>
       <c r="AD9" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>77</v>
@@ -3200,7 +3251,7 @@
         <v>76</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>76</v>
@@ -3217,13 +3268,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B10" t="s" s="2">
         <v>131</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>76</v>
@@ -3245,13 +3296,13 @@
         <v>76</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -3302,7 +3353,7 @@
         <v>76</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>77</v>
@@ -3311,10 +3362,10 @@
         <v>78</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>144</v>
+        <v>76</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>76</v>
@@ -3406,19 +3457,19 @@
         <v>76</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>76</v>
+        <v>135</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="AD11" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>76</v>
+        <v>151</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>77</v>
@@ -3430,7 +3481,7 @@
         <v>76</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>76</v>
@@ -3447,10 +3498,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3473,17 +3524,17 @@
         <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>76</v>
@@ -3520,19 +3571,19 @@
         <v>76</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>77</v>
@@ -3541,33 +3592,33 @@
         <v>78</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AN12" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>76</v>
@@ -3589,17 +3640,17 @@
         <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>76</v>
@@ -3648,7 +3699,7 @@
         <v>76</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>77</v>
@@ -3657,30 +3708,30 @@
         <v>78</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3703,13 +3754,13 @@
         <v>76</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3760,7 +3811,7 @@
         <v>76</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>77</v>
@@ -3781,7 +3832,7 @@
         <v>76</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>76</v>
@@ -3789,10 +3840,10 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3818,10 +3869,10 @@
         <v>132</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="N15" t="s" s="2">
         <v>149</v>
@@ -3865,13 +3916,13 @@
         <v>135</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>178</v>
+        <v>136</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="AF15" t="s" s="2">
         <v>180</v>
@@ -3886,7 +3937,7 @@
         <v>76</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK15" t="s" s="2">
         <v>76</v>
@@ -3895,7 +3946,7 @@
         <v>76</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>76</v>
@@ -4115,7 +4166,7 @@
         <v>87</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ17" t="s" s="2">
         <v>99</v>
@@ -4277,7 +4328,7 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L19" t="s" s="2">
         <v>217</v>
@@ -4399,7 +4450,9 @@
       <c r="M20" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="N20" s="2"/>
+      <c r="N20" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>76</v>
@@ -4448,7 +4501,7 @@
         <v>76</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>77</v>
@@ -4457,19 +4510,19 @@
         <v>87</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>99</v>
+        <v>231</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AN20" t="s" s="2">
         <v>76</v>
@@ -4477,10 +4530,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4503,16 +4556,16 @@
         <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4562,7 +4615,7 @@
         <v>76</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>77</v>
@@ -4571,19 +4624,19 @@
         <v>87</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>99</v>
+        <v>241</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>76</v>
@@ -4591,13 +4644,13 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C22" t="s" s="2">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D22" t="s" s="2">
         <v>76</v>
@@ -4619,17 +4672,17 @@
         <v>88</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>76</v>
@@ -4678,7 +4731,7 @@
         <v>76</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -4687,30 +4740,30 @@
         <v>78</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4733,13 +4786,13 @@
         <v>76</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -4790,7 +4843,7 @@
         <v>76</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>77</v>
@@ -4811,7 +4864,7 @@
         <v>76</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>76</v>
@@ -4819,10 +4872,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4848,10 +4901,10 @@
         <v>132</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="N24" t="s" s="2">
         <v>149</v>
@@ -4895,13 +4948,13 @@
         <v>135</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>178</v>
+        <v>136</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="AF24" t="s" s="2">
         <v>180</v>
@@ -4916,7 +4969,7 @@
         <v>76</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK24" t="s" s="2">
         <v>76</v>
@@ -4925,7 +4978,7 @@
         <v>76</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>76</v>
@@ -4933,7 +4986,7 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B25" t="s" s="2">
         <v>182</v>
@@ -5049,7 +5102,7 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="B26" t="s" s="2">
         <v>193</v>
@@ -5145,7 +5198,7 @@
         <v>87</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ26" t="s" s="2">
         <v>99</v>
@@ -5165,7 +5218,7 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B27" t="s" s="2">
         <v>205</v>
@@ -5210,7 +5263,7 @@
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>76</v>
@@ -5281,7 +5334,7 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>216</v>
@@ -5307,7 +5360,7 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L28" t="s" s="2">
         <v>217</v>
@@ -5395,7 +5448,7 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>225</v>
@@ -5429,7 +5482,9 @@
       <c r="M29" t="s" s="2">
         <v>228</v>
       </c>
-      <c r="N29" s="2"/>
+      <c r="N29" t="s" s="2">
+        <v>229</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>76</v>
@@ -5478,7 +5533,7 @@
         <v>76</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>77</v>
@@ -5487,19 +5542,19 @@
         <v>87</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>99</v>
+        <v>231</v>
       </c>
       <c r="AK29" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>76</v>
@@ -5507,10 +5562,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5533,16 +5588,16 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5592,7 +5647,7 @@
         <v>76</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>77</v>
@@ -5601,19 +5656,19 @@
         <v>87</v>
       </c>
       <c r="AI30" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>99</v>
+        <v>241</v>
       </c>
       <c r="AK30" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>76</v>
@@ -5621,10 +5676,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5650,12 +5705,14 @@
         <v>101</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>256</v>
-      </c>
-      <c r="N31" s="2"/>
+        <v>259</v>
+      </c>
+      <c r="N31" t="s" s="2">
+        <v>260</v>
+      </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>76</v>
@@ -5704,7 +5761,7 @@
         <v>76</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>77</v>
@@ -5719,13 +5776,13 @@
         <v>99</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>76</v>
@@ -5733,10 +5790,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5759,15 +5816,17 @@
         <v>76</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>263</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>267</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>268</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>76</v>
@@ -5816,7 +5875,7 @@
         <v>76</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>77</v>
@@ -5831,13 +5890,13 @@
         <v>99</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="AN32" t="s" s="2">
         <v>76</v>
@@ -5845,10 +5904,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5874,13 +5933,13 @@
         <v>107</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5888,7 +5947,7 @@
       </c>
       <c r="Q33" s="2"/>
       <c r="R33" t="s" s="2">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="S33" t="s" s="2">
         <v>76</v>
@@ -5909,28 +5968,28 @@
         <v>187</v>
       </c>
       <c r="Y33" t="s" s="2">
+        <v>274</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>275</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF33" t="s" s="2">
         <v>269</v>
-      </c>
-      <c r="Z33" t="s" s="2">
-        <v>270</v>
-      </c>
-      <c r="AA33" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB33" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC33" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD33" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE33" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF33" t="s" s="2">
-        <v>264</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>87</v>
@@ -5945,28 +6004,28 @@
         <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>273</v>
+        <v>278</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -5985,17 +6044,19 @@
         <v>76</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>278</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>283</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="O34" t="s" s="2">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>76</v>
@@ -6044,7 +6105,7 @@
         <v>76</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>77</v>
@@ -6053,19 +6114,19 @@
         <v>78</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>99</v>
+        <v>241</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>76</v>
@@ -6073,14 +6134,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6102,12 +6163,14 @@
         <v>194</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>285</v>
-      </c>
-      <c r="N35" s="2"/>
+        <v>291</v>
+      </c>
+      <c r="N35" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
         <v>76</v>
@@ -6132,32 +6195,32 @@
         <v>76</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>287</v>
+        <v>294</v>
       </c>
       <c r="Z35" t="s" s="2">
+        <v>295</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AF35" t="s" s="2">
         <v>288</v>
       </c>
-      <c r="AA35" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AB35" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AC35" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AD35" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AE35" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AF35" t="s" s="2">
-        <v>282</v>
-      </c>
       <c r="AG35" t="s" s="2">
         <v>87</v>
       </c>
@@ -6165,30 +6228,30 @@
         <v>87</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ35" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>289</v>
+        <v>296</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>290</v>
+        <v>297</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>291</v>
+        <v>298</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>292</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>293</v>
+        <v>300</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6211,13 +6274,13 @@
         <v>76</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -6268,7 +6331,7 @@
         <v>76</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>77</v>
@@ -6289,7 +6352,7 @@
         <v>76</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>76</v>
@@ -6297,10 +6360,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6326,10 +6389,10 @@
         <v>132</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="N37" t="s" s="2">
         <v>149</v>
@@ -6373,13 +6436,13 @@
         <v>135</v>
       </c>
       <c r="AC37" t="s" s="2">
-        <v>178</v>
+        <v>136</v>
       </c>
       <c r="AD37" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="AF37" t="s" s="2">
         <v>180</v>
@@ -6394,7 +6457,7 @@
         <v>76</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>76</v>
@@ -6403,7 +6466,7 @@
         <v>76</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>76</v>
@@ -6411,10 +6474,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6437,19 +6500,19 @@
         <v>88</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>296</v>
+        <v>303</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>297</v>
+        <v>304</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>298</v>
+        <v>305</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>76</v>
@@ -6498,7 +6561,7 @@
         <v>76</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>301</v>
+        <v>308</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>77</v>
@@ -6507,7 +6570,7 @@
         <v>78</v>
       </c>
       <c r="AI38" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ38" t="s" s="2">
         <v>99</v>
@@ -6516,10 +6579,10 @@
         <v>76</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>302</v>
+        <v>309</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>303</v>
+        <v>310</v>
       </c>
       <c r="AN38" t="s" s="2">
         <v>76</v>
@@ -6527,10 +6590,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>304</v>
+        <v>311</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6553,13 +6616,13 @@
         <v>76</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6610,7 +6673,7 @@
         <v>76</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>77</v>
@@ -6631,7 +6694,7 @@
         <v>76</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AN39" t="s" s="2">
         <v>76</v>
@@ -6639,10 +6702,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>305</v>
+        <v>312</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6668,10 +6731,10 @@
         <v>132</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="N40" t="s" s="2">
         <v>149</v>
@@ -6715,13 +6778,13 @@
         <v>135</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>178</v>
+        <v>136</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="AF40" t="s" s="2">
         <v>180</v>
@@ -6736,7 +6799,7 @@
         <v>76</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK40" t="s" s="2">
         <v>76</v>
@@ -6745,7 +6808,7 @@
         <v>76</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AN40" t="s" s="2">
         <v>76</v>
@@ -6753,10 +6816,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>306</v>
+        <v>313</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6782,23 +6845,23 @@
         <v>101</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>309</v>
+        <v>316</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q41" s="2"/>
       <c r="R41" t="s" s="2">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="S41" t="s" s="2">
         <v>76</v>
@@ -6840,7 +6903,7 @@
         <v>76</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>312</v>
+        <v>319</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>77</v>
@@ -6858,10 +6921,10 @@
         <v>76</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>314</v>
+        <v>321</v>
       </c>
       <c r="AN41" t="s" s="2">
         <v>76</v>
@@ -6869,10 +6932,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>315</v>
+        <v>322</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6895,16 +6958,16 @@
         <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>317</v>
+        <v>324</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>318</v>
+        <v>325</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6954,7 +7017,7 @@
         <v>76</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>319</v>
+        <v>326</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>77</v>
@@ -6972,10 +7035,10 @@
         <v>76</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>320</v>
+        <v>327</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>321</v>
+        <v>328</v>
       </c>
       <c r="AN42" t="s" s="2">
         <v>76</v>
@@ -6983,10 +7046,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>322</v>
+        <v>329</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7012,21 +7075,21 @@
         <v>107</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>323</v>
+        <v>330</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" t="s" s="2">
-        <v>325</v>
+        <v>332</v>
       </c>
       <c r="P43" t="s" s="2">
         <v>76</v>
       </c>
       <c r="Q43" s="2"/>
       <c r="R43" t="s" s="2">
-        <v>326</v>
+        <v>333</v>
       </c>
       <c r="S43" t="s" s="2">
         <v>76</v>
@@ -7068,7 +7131,7 @@
         <v>76</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>327</v>
+        <v>334</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>77</v>
@@ -7086,10 +7149,10 @@
         <v>76</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>328</v>
+        <v>335</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>329</v>
+        <v>336</v>
       </c>
       <c r="AN43" t="s" s="2">
         <v>76</v>
@@ -7097,10 +7160,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>330</v>
+        <v>337</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7123,17 +7186,19 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>331</v>
+        <v>338</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>332</v>
-      </c>
-      <c r="N44" s="2"/>
+        <v>339</v>
+      </c>
+      <c r="N44" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="O44" t="s" s="2">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>76</v>
@@ -7182,7 +7247,7 @@
         <v>76</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>77</v>
@@ -7200,10 +7265,10 @@
         <v>76</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="AM44" t="s" s="2">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="AN44" t="s" s="2">
         <v>76</v>
@@ -7211,10 +7276,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7237,19 +7302,19 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>76</v>
@@ -7298,7 +7363,7 @@
         <v>76</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>77</v>
@@ -7316,10 +7381,10 @@
         <v>76</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>76</v>
@@ -7327,10 +7392,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7353,19 +7418,19 @@
         <v>88</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>76</v>
@@ -7414,7 +7479,7 @@
         <v>76</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>77</v>
@@ -7432,10 +7497,10 @@
         <v>76</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="AN46" t="s" s="2">
         <v>76</v>
@@ -7443,14 +7508,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7469,17 +7534,19 @@
         <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>358</v>
-      </c>
-      <c r="N47" s="2"/>
+        <v>366</v>
+      </c>
+      <c r="N47" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="O47" t="s" s="2">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>76</v>
@@ -7528,7 +7595,7 @@
         <v>76</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>87</v>
@@ -7537,30 +7604,30 @@
         <v>87</v>
       </c>
       <c r="AI47" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ47" t="s" s="2">
-        <v>99</v>
+        <v>241</v>
       </c>
       <c r="AK47" t="s" s="2">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>363</v>
+        <v>371</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7583,13 +7650,13 @@
         <v>76</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7640,7 +7707,7 @@
         <v>76</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>77</v>
@@ -7661,7 +7728,7 @@
         <v>76</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>76</v>
@@ -7669,10 +7736,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7698,10 +7765,10 @@
         <v>132</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>149</v>
@@ -7745,13 +7812,13 @@
         <v>135</v>
       </c>
       <c r="AC49" t="s" s="2">
-        <v>178</v>
+        <v>136</v>
       </c>
       <c r="AD49" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE49" t="s" s="2">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="AF49" t="s" s="2">
         <v>180</v>
@@ -7766,7 +7833,7 @@
         <v>76</v>
       </c>
       <c r="AJ49" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK49" t="s" s="2">
         <v>76</v>
@@ -7775,7 +7842,7 @@
         <v>76</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>76</v>
@@ -7783,10 +7850,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7809,16 +7876,16 @@
         <v>88</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
@@ -7868,7 +7935,7 @@
         <v>76</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>77</v>
@@ -7877,7 +7944,7 @@
         <v>87</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>99</v>
@@ -7897,10 +7964,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7926,13 +7993,13 @@
         <v>101</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7961,10 +8028,10 @@
         <v>199</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>76</v>
@@ -7982,7 +8049,7 @@
         <v>76</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>77</v>
@@ -8011,10 +8078,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8037,16 +8104,16 @@
         <v>88</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8096,7 +8163,7 @@
         <v>76</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>77</v>
@@ -8105,7 +8172,7 @@
         <v>87</v>
       </c>
       <c r="AI52" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ52" t="s" s="2">
         <v>99</v>
@@ -8114,10 +8181,10 @@
         <v>76</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>76</v>
+        <v>393</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>76</v>
@@ -8125,10 +8192,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>385</v>
+        <v>394</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8151,16 +8218,16 @@
         <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -8210,7 +8277,7 @@
         <v>76</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>77</v>
@@ -8239,14 +8306,14 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="E54" s="2"/>
       <c r="F54" t="s" s="2">
@@ -8265,17 +8332,19 @@
         <v>88</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="N54" s="2"/>
+        <v>403</v>
+      </c>
+      <c r="N54" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="O54" t="s" s="2">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>76</v>
@@ -8324,7 +8393,7 @@
         <v>76</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>77</v>
@@ -8333,34 +8402,34 @@
         <v>87</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ54" t="s" s="2">
-        <v>99</v>
+        <v>241</v>
       </c>
       <c r="AK54" t="s" s="2">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>397</v>
+        <v>406</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>399</v>
+        <v>408</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8379,16 +8448,16 @@
         <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8438,7 +8507,7 @@
         <v>76</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>77</v>
@@ -8447,30 +8516,30 @@
         <v>87</v>
       </c>
       <c r="AI55" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ55" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>408</v>
+        <v>417</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8493,13 +8562,13 @@
         <v>76</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>412</v>
+        <v>421</v>
       </c>
       <c r="N56" s="2"/>
       <c r="O56" s="2"/>
@@ -8550,7 +8619,7 @@
         <v>76</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -8559,19 +8628,19 @@
         <v>78</v>
       </c>
       <c r="AI56" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ56" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="AM56" t="s" s="2">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="AN56" t="s" s="2">
         <v>76</v>
@@ -8579,10 +8648,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8605,13 +8674,13 @@
         <v>76</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -8662,7 +8731,7 @@
         <v>76</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -8683,7 +8752,7 @@
         <v>76</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>76</v>
@@ -8691,10 +8760,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8720,10 +8789,10 @@
         <v>132</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="N58" t="s" s="2">
         <v>149</v>
@@ -8764,16 +8833,16 @@
         <v>76</v>
       </c>
       <c r="AB58" t="s" s="2">
-        <v>76</v>
+        <v>135</v>
       </c>
       <c r="AC58" t="s" s="2">
-        <v>76</v>
+        <v>136</v>
       </c>
       <c r="AD58" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE58" t="s" s="2">
-        <v>76</v>
+        <v>151</v>
       </c>
       <c r="AF58" t="s" s="2">
         <v>180</v>
@@ -8788,7 +8857,7 @@
         <v>76</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>76</v>
@@ -8797,7 +8866,7 @@
         <v>76</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>76</v>
@@ -8805,14 +8874,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>419</v>
+        <v>428</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8834,10 +8903,10 @@
         <v>132</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="N59" t="s" s="2">
         <v>149</v>
@@ -8892,7 +8961,7 @@
         <v>76</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>422</v>
+        <v>431</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>77</v>
@@ -8904,7 +8973,7 @@
         <v>76</v>
       </c>
       <c r="AJ59" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK59" t="s" s="2">
         <v>76</v>
@@ -8921,10 +8990,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8950,12 +9019,14 @@
         <v>194</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>425</v>
-      </c>
-      <c r="N60" s="2"/>
+        <v>434</v>
+      </c>
+      <c r="N60" t="s" s="2">
+        <v>292</v>
+      </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
         <v>76</v>
@@ -8980,13 +9051,13 @@
         <v>76</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>76</v>
@@ -9004,7 +9075,7 @@
         <v>76</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
@@ -9013,19 +9084,19 @@
         <v>87</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>429</v>
+        <v>438</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>76</v>
@@ -9033,10 +9104,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9059,15 +9130,17 @@
         <v>76</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>431</v>
+        <v>440</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>432</v>
+        <v>441</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>433</v>
-      </c>
-      <c r="N61" s="2"/>
+        <v>442</v>
+      </c>
+      <c r="N61" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
         <v>76</v>
@@ -9116,7 +9189,7 @@
         <v>76</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>430</v>
+        <v>439</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>87</v>
@@ -9125,30 +9198,30 @@
         <v>87</v>
       </c>
       <c r="AI61" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ61" t="s" s="2">
-        <v>99</v>
+        <v>241</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>436</v>
+        <v>445</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9171,16 +9244,16 @@
         <v>76</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>439</v>
+        <v>448</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>440</v>
+        <v>449</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9230,7 +9303,7 @@
         <v>76</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>437</v>
+        <v>446</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>77</v>
@@ -9239,19 +9312,19 @@
         <v>87</v>
       </c>
       <c r="AI62" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ62" t="s" s="2">
-        <v>99</v>
+        <v>241</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>434</v>
+        <v>443</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>130</v>
       </c>
       <c r="AM62" t="s" s="2">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="AN62" t="s" s="2">
         <v>76</v>
@@ -9259,10 +9332,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9285,16 +9358,16 @@
         <v>76</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>443</v>
+        <v>452</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>444</v>
+        <v>453</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>445</v>
+        <v>454</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9344,7 +9417,7 @@
         <v>76</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>442</v>
+        <v>451</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
@@ -9353,10 +9426,10 @@
         <v>87</v>
       </c>
       <c r="AI63" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>99</v>
+        <v>241</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>76</v>
@@ -9365,7 +9438,7 @@
         <v>130</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>441</v>
+        <v>450</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>76</v>
@@ -9373,10 +9446,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9399,16 +9472,16 @@
         <v>76</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>447</v>
+        <v>456</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>448</v>
+        <v>457</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>449</v>
+        <v>458</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9458,7 +9531,7 @@
         <v>76</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>446</v>
+        <v>455</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
@@ -9467,19 +9540,19 @@
         <v>87</v>
       </c>
       <c r="AI64" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ64" t="s" s="2">
-        <v>99</v>
+        <v>241</v>
       </c>
       <c r="AK64" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>450</v>
+        <v>459</v>
       </c>
       <c r="AM64" t="s" s="2">
-        <v>76</v>
+        <v>460</v>
       </c>
       <c r="AN64" t="s" s="2">
         <v>76</v>
@@ -9487,10 +9560,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9513,16 +9586,16 @@
         <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>453</v>
+        <v>463</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>454</v>
+        <v>464</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>455</v>
+        <v>465</v>
       </c>
       <c r="O65" s="2"/>
       <c r="P65" t="s" s="2">
@@ -9572,7 +9645,7 @@
         <v>76</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>451</v>
+        <v>461</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>77</v>
@@ -9581,19 +9654,19 @@
         <v>87</v>
       </c>
       <c r="AI65" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ65" t="s" s="2">
-        <v>99</v>
+        <v>466</v>
       </c>
       <c r="AK65" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="AM65" t="s" s="2">
-        <v>76</v>
+        <v>468</v>
       </c>
       <c r="AN65" t="s" s="2">
         <v>76</v>
@@ -9601,10 +9674,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9630,13 +9703,13 @@
         <v>194</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -9662,13 +9735,13 @@
         <v>76</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>76</v>
@@ -9686,7 +9759,7 @@
         <v>76</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>77</v>
@@ -9695,7 +9768,7 @@
         <v>78</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ66" t="s" s="2">
         <v>99</v>
@@ -9704,10 +9777,10 @@
         <v>76</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>76</v>
+        <v>475</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>76</v>
@@ -9715,10 +9788,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9741,16 +9814,16 @@
         <v>76</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>465</v>
+        <v>478</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>466</v>
+        <v>479</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>467</v>
+        <v>480</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>468</v>
+        <v>481</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9800,7 +9873,7 @@
         <v>76</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>464</v>
+        <v>477</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>77</v>
@@ -9818,7 +9891,7 @@
         <v>76</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>469</v>
+        <v>482</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>76</v>
@@ -9829,10 +9902,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9855,16 +9928,16 @@
         <v>76</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>471</v>
+        <v>484</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>472</v>
+        <v>485</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>473</v>
+        <v>486</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>474</v>
+        <v>487</v>
       </c>
       <c r="O68" s="2"/>
       <c r="P68" t="s" s="2">
@@ -9914,7 +9987,7 @@
         <v>76</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>77</v>
@@ -9923,7 +9996,7 @@
         <v>87</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>99</v>
@@ -9932,10 +10005,10 @@
         <v>76</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>475</v>
+        <v>488</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>76</v>
+        <v>489</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>76</v>
@@ -9943,10 +10016,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>476</v>
+        <v>490</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>476</v>
+        <v>490</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9969,16 +10042,16 @@
         <v>76</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>477</v>
+        <v>491</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>478</v>
+        <v>492</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>479</v>
+        <v>493</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -10028,7 +10101,7 @@
         <v>76</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>476</v>
+        <v>490</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>77</v>
@@ -10057,10 +10130,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>480</v>
+        <v>494</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>480</v>
+        <v>494</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10083,16 +10156,16 @@
         <v>88</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>481</v>
+        <v>495</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>482</v>
+        <v>496</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>483</v>
+        <v>497</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>484</v>
+        <v>498</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10142,7 +10215,7 @@
         <v>76</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>480</v>
+        <v>494</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>77</v>
@@ -10151,30 +10224,30 @@
         <v>87</v>
       </c>
       <c r="AI70" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ70" t="s" s="2">
-        <v>99</v>
+        <v>241</v>
       </c>
       <c r="AK70" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>435</v>
+        <v>444</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>436</v>
+        <v>445</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>485</v>
+        <v>499</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>485</v>
+        <v>499</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10197,13 +10270,13 @@
         <v>76</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10254,7 +10327,7 @@
         <v>76</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
@@ -10275,7 +10348,7 @@
         <v>76</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>76</v>
@@ -10283,10 +10356,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>486</v>
+        <v>500</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>486</v>
+        <v>500</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10312,10 +10385,10 @@
         <v>132</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>149</v>
@@ -10359,13 +10432,13 @@
         <v>135</v>
       </c>
       <c r="AC72" t="s" s="2">
-        <v>178</v>
+        <v>136</v>
       </c>
       <c r="AD72" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE72" t="s" s="2">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="AF72" t="s" s="2">
         <v>180</v>
@@ -10380,7 +10453,7 @@
         <v>76</v>
       </c>
       <c r="AJ72" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK72" t="s" s="2">
         <v>76</v>
@@ -10389,7 +10462,7 @@
         <v>76</v>
       </c>
       <c r="AM72" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AN72" t="s" s="2">
         <v>76</v>
@@ -10397,10 +10470,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>487</v>
+        <v>501</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>487</v>
+        <v>501</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10423,16 +10496,16 @@
         <v>88</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10482,7 +10555,7 @@
         <v>76</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>77</v>
@@ -10491,7 +10564,7 @@
         <v>87</v>
       </c>
       <c r="AI73" t="s" s="2">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="AJ73" t="s" s="2">
         <v>99</v>
@@ -10511,10 +10584,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>488</v>
+        <v>502</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>488</v>
+        <v>502</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10540,13 +10613,13 @@
         <v>101</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10575,10 +10648,10 @@
         <v>199</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>76</v>
@@ -10596,7 +10669,7 @@
         <v>76</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>77</v>
@@ -10625,10 +10698,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>489</v>
+        <v>503</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>489</v>
+        <v>503</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10651,16 +10724,16 @@
         <v>88</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>490</v>
+        <v>504</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10710,7 +10783,7 @@
         <v>76</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>77</v>
@@ -10719,7 +10792,7 @@
         <v>87</v>
       </c>
       <c r="AI75" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ75" t="s" s="2">
         <v>99</v>
@@ -10728,10 +10801,10 @@
         <v>76</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>76</v>
+        <v>393</v>
       </c>
       <c r="AM75" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AN75" t="s" s="2">
         <v>76</v>
@@ -10739,10 +10812,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>491</v>
+        <v>505</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>491</v>
+        <v>505</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10765,16 +10838,16 @@
         <v>88</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10824,7 +10897,7 @@
         <v>76</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>77</v>
@@ -10853,10 +10926,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>492</v>
+        <v>506</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>492</v>
+        <v>506</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10879,16 +10952,16 @@
         <v>88</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>493</v>
+        <v>507</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>494</v>
+        <v>508</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>495</v>
+        <v>509</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>496</v>
+        <v>510</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -10938,7 +11011,7 @@
         <v>76</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>492</v>
+        <v>506</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>77</v>
@@ -10967,10 +11040,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>497</v>
+        <v>511</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>497</v>
+        <v>511</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10996,13 +11069,13 @@
         <v>194</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>498</v>
+        <v>512</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>499</v>
+        <v>513</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>500</v>
+        <v>514</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -11028,13 +11101,13 @@
         <v>76</v>
       </c>
       <c r="X78" t="s" s="2">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="Y78" t="s" s="2">
-        <v>501</v>
+        <v>515</v>
       </c>
       <c r="Z78" t="s" s="2">
-        <v>502</v>
+        <v>516</v>
       </c>
       <c r="AA78" t="s" s="2">
         <v>76</v>
@@ -11052,7 +11125,7 @@
         <v>76</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>497</v>
+        <v>511</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>77</v>
@@ -11061,30 +11134,30 @@
         <v>78</v>
       </c>
       <c r="AI78" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ78" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>503</v>
+        <v>517</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>504</v>
+        <v>518</v>
       </c>
       <c r="AM78" t="s" s="2">
-        <v>505</v>
+        <v>519</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>506</v>
+        <v>520</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>507</v>
+        <v>521</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>507</v>
+        <v>521</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11107,15 +11180,17 @@
         <v>76</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>508</v>
+        <v>522</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>509</v>
+        <v>523</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>510</v>
-      </c>
-      <c r="N79" s="2"/>
+        <v>524</v>
+      </c>
+      <c r="N79" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="O79" s="2"/>
       <c r="P79" t="s" s="2">
         <v>76</v>
@@ -11164,7 +11239,7 @@
         <v>76</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>507</v>
+        <v>521</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>77</v>
@@ -11173,30 +11248,30 @@
         <v>78</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ79" t="s" s="2">
-        <v>99</v>
+        <v>241</v>
       </c>
       <c r="AK79" t="s" s="2">
-        <v>511</v>
+        <v>525</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>504</v>
+        <v>518</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>512</v>
+        <v>526</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>506</v>
+        <v>520</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>513</v>
+        <v>527</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>513</v>
+        <v>527</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11219,13 +11294,13 @@
         <v>76</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>514</v>
+        <v>528</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>515</v>
+        <v>529</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>516</v>
+        <v>530</v>
       </c>
       <c r="N80" s="2"/>
       <c r="O80" s="2"/>
@@ -11252,13 +11327,13 @@
         <v>76</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>286</v>
+        <v>293</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>517</v>
+        <v>531</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>518</v>
+        <v>532</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>76</v>
@@ -11276,7 +11351,7 @@
         <v>76</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>513</v>
+        <v>527</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>77</v>
@@ -11285,7 +11360,7 @@
         <v>87</v>
       </c>
       <c r="AI80" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ80" t="s" s="2">
         <v>99</v>
@@ -11297,7 +11372,7 @@
         <v>76</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>519</v>
+        <v>533</v>
       </c>
       <c r="AN80" t="s" s="2">
         <v>76</v>
@@ -11305,10 +11380,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>520</v>
+        <v>534</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>520</v>
+        <v>534</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11331,16 +11406,16 @@
         <v>88</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>521</v>
+        <v>535</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>522</v>
+        <v>536</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>523</v>
+        <v>537</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>524</v>
+        <v>538</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11390,7 +11465,7 @@
         <v>76</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>520</v>
+        <v>534</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>77</v>
@@ -11399,10 +11474,10 @@
         <v>78</v>
       </c>
       <c r="AI81" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ81" t="s" s="2">
-        <v>99</v>
+        <v>241</v>
       </c>
       <c r="AK81" t="s" s="2">
         <v>76</v>
@@ -11411,7 +11486,7 @@
         <v>76</v>
       </c>
       <c r="AM81" t="s" s="2">
-        <v>76</v>
+        <v>460</v>
       </c>
       <c r="AN81" t="s" s="2">
         <v>76</v>
@@ -11419,10 +11494,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>525</v>
+        <v>539</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>525</v>
+        <v>539</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11445,15 +11520,17 @@
         <v>76</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>526</v>
+        <v>540</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>527</v>
+        <v>541</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>528</v>
-      </c>
-      <c r="N82" s="2"/>
+        <v>542</v>
+      </c>
+      <c r="N82" t="s" s="2">
+        <v>543</v>
+      </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
         <v>76</v>
@@ -11502,7 +11579,7 @@
         <v>76</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>525</v>
+        <v>539</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>77</v>
@@ -11511,19 +11588,19 @@
         <v>78</v>
       </c>
       <c r="AI82" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ82" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK82" t="s" s="2">
-        <v>529</v>
+        <v>544</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>530</v>
+        <v>545</v>
       </c>
       <c r="AM82" t="s" s="2">
-        <v>531</v>
+        <v>546</v>
       </c>
       <c r="AN82" t="s" s="2">
         <v>76</v>
@@ -11531,10 +11608,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>532</v>
+        <v>547</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>532</v>
+        <v>547</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11545,7 +11622,7 @@
         <v>77</v>
       </c>
       <c r="G83" t="s" s="2">
-        <v>533</v>
+        <v>548</v>
       </c>
       <c r="H83" t="s" s="2">
         <v>88</v>
@@ -11557,15 +11634,17 @@
         <v>76</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>534</v>
+        <v>549</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>535</v>
+        <v>550</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>536</v>
-      </c>
-      <c r="N83" s="2"/>
+        <v>551</v>
+      </c>
+      <c r="N83" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="O83" s="2"/>
       <c r="P83" t="s" s="2">
         <v>76</v>
@@ -11602,17 +11681,17 @@
         <v>76</v>
       </c>
       <c r="AB83" t="s" s="2">
-        <v>537</v>
+        <v>552</v>
       </c>
       <c r="AC83" s="2"/>
       <c r="AD83" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE83" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>532</v>
+        <v>547</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>77</v>
@@ -11621,33 +11700,33 @@
         <v>78</v>
       </c>
       <c r="AI83" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ83" t="s" s="2">
-        <v>99</v>
+        <v>241</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>538</v>
+        <v>553</v>
       </c>
       <c r="AL83" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>76</v>
+        <v>460</v>
       </c>
       <c r="AN83" t="s" s="2">
         <v>76</v>
       </c>
     </row>
-    <row r="84" hidden="true">
+    <row r="84">
       <c r="A84" t="s" s="2">
-        <v>539</v>
+        <v>554</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>532</v>
+        <v>547</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>540</v>
+        <v>555</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>76</v>
@@ -11660,7 +11739,7 @@
         <v>87</v>
       </c>
       <c r="H84" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I84" t="s" s="2">
         <v>76</v>
@@ -11669,15 +11748,17 @@
         <v>76</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>541</v>
+        <v>556</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>535</v>
+        <v>550</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="N84" s="2"/>
+        <v>557</v>
+      </c>
+      <c r="N84" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
         <v>76</v>
@@ -11726,7 +11807,7 @@
         <v>76</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>532</v>
+        <v>547</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>77</v>
@@ -11735,19 +11816,19 @@
         <v>78</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>99</v>
+        <v>241</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>538</v>
+        <v>553</v>
       </c>
       <c r="AL84" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM84" t="s" s="2">
-        <v>76</v>
+        <v>460</v>
       </c>
       <c r="AN84" t="s" s="2">
         <v>76</v>
@@ -11755,10 +11836,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>543</v>
+        <v>558</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>544</v>
+        <v>559</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11781,13 +11862,13 @@
         <v>76</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11838,7 +11919,7 @@
         <v>76</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>77</v>
@@ -11859,7 +11940,7 @@
         <v>76</v>
       </c>
       <c r="AM85" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AN85" t="s" s="2">
         <v>76</v>
@@ -11867,10 +11948,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>545</v>
+        <v>560</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>546</v>
+        <v>561</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11896,10 +11977,10 @@
         <v>132</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="N86" t="s" s="2">
         <v>149</v>
@@ -11943,13 +12024,13 @@
         <v>135</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>178</v>
+        <v>136</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="AF86" t="s" s="2">
         <v>180</v>
@@ -11964,7 +12045,7 @@
         <v>76</v>
       </c>
       <c r="AJ86" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK86" t="s" s="2">
         <v>76</v>
@@ -11973,7 +12054,7 @@
         <v>76</v>
       </c>
       <c r="AM86" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AN86" t="s" s="2">
         <v>76</v>
@@ -11981,10 +12062,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>547</v>
+        <v>562</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>548</v>
+        <v>563</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12007,16 +12088,16 @@
         <v>88</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="O87" s="2"/>
       <c r="P87" t="s" s="2">
@@ -12066,7 +12147,7 @@
         <v>76</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>77</v>
@@ -12075,7 +12156,7 @@
         <v>87</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>99</v>
@@ -12095,10 +12176,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>549</v>
+        <v>564</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>550</v>
+        <v>565</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12124,13 +12205,13 @@
         <v>101</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12159,10 +12240,10 @@
         <v>199</v>
       </c>
       <c r="Y88" t="s" s="2">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="Z88" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="AA88" t="s" s="2">
         <v>76</v>
@@ -12180,7 +12261,7 @@
         <v>76</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>77</v>
@@ -12209,10 +12290,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>551</v>
+        <v>566</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>552</v>
+        <v>567</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12235,16 +12316,16 @@
         <v>88</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -12294,7 +12375,7 @@
         <v>76</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>77</v>
@@ -12303,7 +12384,7 @@
         <v>87</v>
       </c>
       <c r="AI89" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ89" t="s" s="2">
         <v>99</v>
@@ -12312,10 +12393,10 @@
         <v>76</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>76</v>
+        <v>393</v>
       </c>
       <c r="AM89" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AN89" t="s" s="2">
         <v>76</v>
@@ -12323,10 +12404,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>553</v>
+        <v>568</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>554</v>
+        <v>569</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12349,16 +12430,16 @@
         <v>88</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="O90" s="2"/>
       <c r="P90" t="s" s="2">
@@ -12366,7 +12447,7 @@
       </c>
       <c r="Q90" s="2"/>
       <c r="R90" t="s" s="2">
-        <v>555</v>
+        <v>570</v>
       </c>
       <c r="S90" t="s" s="2">
         <v>76</v>
@@ -12408,7 +12489,7 @@
         <v>76</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>77</v>
@@ -12435,15 +12516,15 @@
         <v>76</v>
       </c>
     </row>
-    <row r="91" hidden="true">
+    <row r="91">
       <c r="A91" t="s" s="2">
-        <v>556</v>
+        <v>571</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>532</v>
+        <v>547</v>
       </c>
       <c r="C91" t="s" s="2">
-        <v>557</v>
+        <v>572</v>
       </c>
       <c r="D91" t="s" s="2">
         <v>76</v>
@@ -12456,7 +12537,7 @@
         <v>87</v>
       </c>
       <c r="H91" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I91" t="s" s="2">
         <v>76</v>
@@ -12465,15 +12546,17 @@
         <v>76</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>558</v>
+        <v>573</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>535</v>
+        <v>550</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="N91" s="2"/>
+        <v>557</v>
+      </c>
+      <c r="N91" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
         <v>76</v>
@@ -12522,7 +12605,7 @@
         <v>76</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>532</v>
+        <v>547</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>77</v>
@@ -12531,19 +12614,19 @@
         <v>78</v>
       </c>
       <c r="AI91" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ91" t="s" s="2">
-        <v>99</v>
+        <v>241</v>
       </c>
       <c r="AK91" t="s" s="2">
-        <v>538</v>
+        <v>553</v>
       </c>
       <c r="AL91" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM91" t="s" s="2">
-        <v>76</v>
+        <v>460</v>
       </c>
       <c r="AN91" t="s" s="2">
         <v>76</v>
@@ -12551,10 +12634,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
+        <v>574</v>
+      </c>
+      <c r="B92" t="s" s="2">
         <v>559</v>
-      </c>
-      <c r="B92" t="s" s="2">
-        <v>544</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12577,13 +12660,13 @@
         <v>76</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -12634,7 +12717,7 @@
         <v>76</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>77</v>
@@ -12655,7 +12738,7 @@
         <v>76</v>
       </c>
       <c r="AM92" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AN92" t="s" s="2">
         <v>76</v>
@@ -12663,10 +12746,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>560</v>
+        <v>575</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>546</v>
+        <v>561</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12692,10 +12775,10 @@
         <v>132</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="N93" t="s" s="2">
         <v>149</v>
@@ -12739,13 +12822,13 @@
         <v>135</v>
       </c>
       <c r="AC93" t="s" s="2">
-        <v>178</v>
+        <v>136</v>
       </c>
       <c r="AD93" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE93" t="s" s="2">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="AF93" t="s" s="2">
         <v>180</v>
@@ -12760,7 +12843,7 @@
         <v>76</v>
       </c>
       <c r="AJ93" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK93" t="s" s="2">
         <v>76</v>
@@ -12769,7 +12852,7 @@
         <v>76</v>
       </c>
       <c r="AM93" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AN93" t="s" s="2">
         <v>76</v>
@@ -12777,10 +12860,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>561</v>
+        <v>576</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>548</v>
+        <v>563</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12803,16 +12886,16 @@
         <v>88</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -12862,7 +12945,7 @@
         <v>76</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>77</v>
@@ -12871,7 +12954,7 @@
         <v>87</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="AJ94" t="s" s="2">
         <v>99</v>
@@ -12891,10 +12974,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>562</v>
+        <v>577</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>550</v>
+        <v>565</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -12920,13 +13003,13 @@
         <v>101</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="O95" s="2"/>
       <c r="P95" t="s" s="2">
@@ -12955,10 +13038,10 @@
         <v>199</v>
       </c>
       <c r="Y95" t="s" s="2">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="Z95" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="AA95" t="s" s="2">
         <v>76</v>
@@ -12976,7 +13059,7 @@
         <v>76</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>77</v>
@@ -13005,10 +13088,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>563</v>
+        <v>578</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>552</v>
+        <v>567</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13031,16 +13114,16 @@
         <v>88</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="O96" s="2"/>
       <c r="P96" t="s" s="2">
@@ -13090,7 +13173,7 @@
         <v>76</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>77</v>
@@ -13099,7 +13182,7 @@
         <v>87</v>
       </c>
       <c r="AI96" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ96" t="s" s="2">
         <v>99</v>
@@ -13108,10 +13191,10 @@
         <v>76</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>76</v>
+        <v>393</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AN96" t="s" s="2">
         <v>76</v>
@@ -13119,10 +13202,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>564</v>
+        <v>579</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>554</v>
+        <v>569</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13145,16 +13228,16 @@
         <v>88</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -13162,7 +13245,7 @@
       </c>
       <c r="Q97" s="2"/>
       <c r="R97" t="s" s="2">
-        <v>565</v>
+        <v>580</v>
       </c>
       <c r="S97" t="s" s="2">
         <v>76</v>
@@ -13204,7 +13287,7 @@
         <v>76</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>77</v>
@@ -13231,15 +13314,15 @@
         <v>76</v>
       </c>
     </row>
-    <row r="98" hidden="true">
+    <row r="98">
       <c r="A98" t="s" s="2">
-        <v>566</v>
+        <v>581</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>532</v>
+        <v>547</v>
       </c>
       <c r="C98" t="s" s="2">
-        <v>567</v>
+        <v>582</v>
       </c>
       <c r="D98" t="s" s="2">
         <v>76</v>
@@ -13252,7 +13335,7 @@
         <v>87</v>
       </c>
       <c r="H98" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I98" t="s" s="2">
         <v>76</v>
@@ -13261,15 +13344,17 @@
         <v>76</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>541</v>
+        <v>556</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>535</v>
+        <v>550</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="N98" s="2"/>
+        <v>557</v>
+      </c>
+      <c r="N98" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
         <v>76</v>
@@ -13318,7 +13403,7 @@
         <v>76</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>532</v>
+        <v>547</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>77</v>
@@ -13327,19 +13412,19 @@
         <v>78</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ98" t="s" s="2">
-        <v>99</v>
+        <v>241</v>
       </c>
       <c r="AK98" t="s" s="2">
-        <v>538</v>
+        <v>553</v>
       </c>
       <c r="AL98" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>76</v>
+        <v>460</v>
       </c>
       <c r="AN98" t="s" s="2">
         <v>76</v>
@@ -13347,10 +13432,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>568</v>
+        <v>583</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>544</v>
+        <v>559</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13373,13 +13458,13 @@
         <v>76</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13430,7 +13515,7 @@
         <v>76</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>77</v>
@@ -13451,7 +13536,7 @@
         <v>76</v>
       </c>
       <c r="AM99" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AN99" t="s" s="2">
         <v>76</v>
@@ -13459,10 +13544,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>569</v>
+        <v>584</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>546</v>
+        <v>561</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13488,10 +13573,10 @@
         <v>132</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="N100" t="s" s="2">
         <v>149</v>
@@ -13535,13 +13620,13 @@
         <v>135</v>
       </c>
       <c r="AC100" t="s" s="2">
-        <v>178</v>
+        <v>136</v>
       </c>
       <c r="AD100" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE100" t="s" s="2">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="AF100" t="s" s="2">
         <v>180</v>
@@ -13556,7 +13641,7 @@
         <v>76</v>
       </c>
       <c r="AJ100" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK100" t="s" s="2">
         <v>76</v>
@@ -13565,7 +13650,7 @@
         <v>76</v>
       </c>
       <c r="AM100" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AN100" t="s" s="2">
         <v>76</v>
@@ -13573,10 +13658,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>570</v>
+        <v>585</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>548</v>
+        <v>563</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13599,16 +13684,16 @@
         <v>88</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="O101" s="2"/>
       <c r="P101" t="s" s="2">
@@ -13658,7 +13743,7 @@
         <v>76</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>77</v>
@@ -13667,7 +13752,7 @@
         <v>87</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>99</v>
@@ -13687,10 +13772,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>571</v>
+        <v>586</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>550</v>
+        <v>565</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13716,13 +13801,13 @@
         <v>101</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="O102" s="2"/>
       <c r="P102" t="s" s="2">
@@ -13751,10 +13836,10 @@
         <v>199</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>76</v>
@@ -13772,7 +13857,7 @@
         <v>76</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>77</v>
@@ -13801,10 +13886,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>572</v>
+        <v>587</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>552</v>
+        <v>567</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13827,16 +13912,16 @@
         <v>88</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="O103" s="2"/>
       <c r="P103" t="s" s="2">
@@ -13886,7 +13971,7 @@
         <v>76</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>77</v>
@@ -13895,7 +13980,7 @@
         <v>87</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>99</v>
@@ -13904,10 +13989,10 @@
         <v>76</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>76</v>
+        <v>393</v>
       </c>
       <c r="AM103" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AN103" t="s" s="2">
         <v>76</v>
@@ -13915,10 +14000,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>573</v>
+        <v>588</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>554</v>
+        <v>569</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13941,16 +14026,16 @@
         <v>88</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -13958,7 +14043,7 @@
       </c>
       <c r="Q104" s="2"/>
       <c r="R104" t="s" s="2">
-        <v>574</v>
+        <v>589</v>
       </c>
       <c r="S104" t="s" s="2">
         <v>76</v>
@@ -14000,7 +14085,7 @@
         <v>76</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>77</v>
@@ -14027,15 +14112,15 @@
         <v>76</v>
       </c>
     </row>
-    <row r="105" hidden="true">
+    <row r="105">
       <c r="A105" t="s" s="2">
-        <v>575</v>
+        <v>590</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>532</v>
+        <v>547</v>
       </c>
       <c r="C105" t="s" s="2">
-        <v>576</v>
+        <v>591</v>
       </c>
       <c r="D105" t="s" s="2">
         <v>76</v>
@@ -14048,7 +14133,7 @@
         <v>87</v>
       </c>
       <c r="H105" t="s" s="2">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="I105" t="s" s="2">
         <v>76</v>
@@ -14057,15 +14142,17 @@
         <v>76</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>541</v>
+        <v>556</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>535</v>
+        <v>550</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>542</v>
-      </c>
-      <c r="N105" s="2"/>
+        <v>557</v>
+      </c>
+      <c r="N105" t="s" s="2">
+        <v>284</v>
+      </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
         <v>76</v>
@@ -14114,7 +14201,7 @@
         <v>76</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>532</v>
+        <v>547</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>77</v>
@@ -14123,19 +14210,19 @@
         <v>78</v>
       </c>
       <c r="AI105" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ105" t="s" s="2">
-        <v>99</v>
+        <v>241</v>
       </c>
       <c r="AK105" t="s" s="2">
-        <v>538</v>
+        <v>553</v>
       </c>
       <c r="AL105" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AM105" t="s" s="2">
-        <v>76</v>
+        <v>460</v>
       </c>
       <c r="AN105" t="s" s="2">
         <v>76</v>
@@ -14143,10 +14230,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>577</v>
+        <v>592</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>544</v>
+        <v>559</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14169,13 +14256,13 @@
         <v>76</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -14226,7 +14313,7 @@
         <v>76</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>77</v>
@@ -14247,7 +14334,7 @@
         <v>76</v>
       </c>
       <c r="AM106" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AN106" t="s" s="2">
         <v>76</v>
@@ -14255,10 +14342,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>578</v>
+        <v>593</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>546</v>
+        <v>561</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14284,10 +14371,10 @@
         <v>132</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="N107" t="s" s="2">
         <v>149</v>
@@ -14331,13 +14418,13 @@
         <v>135</v>
       </c>
       <c r="AC107" t="s" s="2">
-        <v>178</v>
+        <v>136</v>
       </c>
       <c r="AD107" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AE107" t="s" s="2">
-        <v>179</v>
+        <v>151</v>
       </c>
       <c r="AF107" t="s" s="2">
         <v>180</v>
@@ -14352,7 +14439,7 @@
         <v>76</v>
       </c>
       <c r="AJ107" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AK107" t="s" s="2">
         <v>76</v>
@@ -14361,7 +14448,7 @@
         <v>76</v>
       </c>
       <c r="AM107" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="AN107" t="s" s="2">
         <v>76</v>
@@ -14369,10 +14456,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>579</v>
+        <v>594</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>548</v>
+        <v>563</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14395,16 +14482,16 @@
         <v>88</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -14454,7 +14541,7 @@
         <v>76</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>77</v>
@@ -14463,7 +14550,7 @@
         <v>87</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>99</v>
@@ -14483,10 +14570,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>580</v>
+        <v>595</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>550</v>
+        <v>565</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14512,13 +14599,13 @@
         <v>101</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -14547,10 +14634,10 @@
         <v>199</v>
       </c>
       <c r="Y109" t="s" s="2">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="Z109" t="s" s="2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="AA109" t="s" s="2">
         <v>76</v>
@@ -14568,7 +14655,7 @@
         <v>76</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>77</v>
@@ -14597,10 +14684,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>581</v>
+        <v>596</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>552</v>
+        <v>567</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14623,16 +14710,16 @@
         <v>88</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -14682,7 +14769,7 @@
         <v>76</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>77</v>
@@ -14691,7 +14778,7 @@
         <v>87</v>
       </c>
       <c r="AI110" t="s" s="2">
-        <v>76</v>
+        <v>160</v>
       </c>
       <c r="AJ110" t="s" s="2">
         <v>99</v>
@@ -14700,10 +14787,10 @@
         <v>76</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>76</v>
+        <v>393</v>
       </c>
       <c r="AM110" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AN110" t="s" s="2">
         <v>76</v>
@@ -14711,10 +14798,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>582</v>
+        <v>597</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>554</v>
+        <v>569</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14737,16 +14824,16 @@
         <v>88</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -14754,7 +14841,7 @@
       </c>
       <c r="Q111" s="2"/>
       <c r="R111" t="s" s="2">
-        <v>583</v>
+        <v>598</v>
       </c>
       <c r="S111" t="s" s="2">
         <v>76</v>
@@ -14796,7 +14883,7 @@
         <v>76</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>77</v>
